--- a/docs/upstream/manual-regression-checklist-updated.xlsx
+++ b/docs/upstream/manual-regression-checklist-updated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Run info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$G$147</definedName>

--- a/docs/upstream/manual-regression-checklist-updated.xlsx
+++ b/docs/upstream/manual-regression-checklist-updated.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$G$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$G$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>After a Copilot reply finishes, scrolling the thread does not turn ordinary `*` characters or unfinished markdown into bold.</t>
+          <t>On Local, fork a finished reply (“Fork in new chat”). The new chat opens, its title starts with `Fork |`, and it contains the messages up to that reply. There is no “Failed to fork chat” toast. On Cloud, with `COPILOT_API_KEY` set, the same action still succeeds.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Ask Copilot for a fixed sequence: today’s calendar, unread Gmail, Slack messages, then a written briefing. The canvas gets `google_calendar_v2`, `gmail_v2`, and `slack` as their own blocks in that order. Those integrations are not attached as Agent tools. A daily time trigger is a `schedule` block, not `schedule_trigger`.</t>
+          <t>After a Copilot reply finishes, scrolling the thread does not turn ordinary `*` characters or unfinished markdown into bold.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Ask Copilot to create an HTML page. The saved file opens as a complete page, not a truncated tag dump in the chat.</t>
+          <t>Ask Copilot for a fixed sequence: today’s calendar, unread Gmail, Slack messages, then a written briefing. The canvas gets `google_calendar_v2`, `gmail_v2`, and `slack` as their own blocks in that order. Those integrations are not attached as Agent tools. A daily time trigger is a `schedule` block, not `schedule_trigger`.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Local-only users stay on Local without the switch.</t>
+          <t>Ask Copilot to create an HTML page. The saved file opens as a complete page, not a truncated tag dump in the chat.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Copilot can generate images and create files; Local image/file usage lands on the Arena ledger.</t>
+          <t>Local-only users stay on Local without the switch.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Floating workflow chat streams a run, including chart and image output.</t>
+          <t>Copilot can generate images and create files; Local image/file usage lands on the Arena ledger.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Deploy-modal chat preview matches the deployed agent.</t>
+          <t>Floating workflow chat streams a run, including chart and image output.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Billing and workspaces (P0)</t>
+          <t>Workspace chat and Local / Cloud copilot (P0)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Arena plans show in upgrade: Starter, Pro, Max (flat org pricing). Checkout ignores the Starter Stripe id.</t>
+          <t>Deploy-modal chat preview matches the deployed agent.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Paying supersedes Starter. Client-org Starter provisioning still runs.</t>
+          <t>Arena plans show in upgrade: Starter, Pro, Max (flat org pricing). Checkout ignores the Starter Stripe id.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Credits-per-dollar and remaining credits: start from a known balance, run one Agent turn, confirm the usage dashboard debit matches the ledger entry.</t>
+          <t>Paying supersedes Starter. Client-org Starter provisioning still runs.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Cost block: an explicit Cost block amount shows once on the run’s usage (no double charge vs the Agent model cost).</t>
+          <t>Credits-per-dollar and remaining credits: start from a known balance, run one Agent turn, confirm the usage dashboard debit matches the ledger entry.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Usage-log multiplier: a metered tool run writes one scaled ledger row, not a raw plus scaled duplicate.</t>
+          <t>Cost block: an explicit Cost block amount shows once on the run’s usage (no double charge vs the Agent model cost).</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Org admin can open billing. A non-admin cannot.</t>
+          <t>Usage-log multiplier: a metered tool run writes one scaled ledger row, not a raw plus scaled duplicate.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Deploy-modal API samples include `X-Sim-Email`. Execute the workflow API with that header set to a Sim user in another organization: the run bills that user’s org, the owning workspace does not also debit it, and Usage for the billed org shows a By Agent row (workflow, owning org · workspace, Run by). A missing header or malformed email is rejected with 400. An email that matches no user is rejected with 400 and `BILLING_EMAIL_NOT_FOUND`. Remaining credits for the billed org drop by that run.</t>
+          <t>Org admin can open billing. A non-admin cannot.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Signup still creates a personal workspace. `/workspace` fallback still lands somewhere valid.</t>
+          <t>Deploy-modal API samples include `X-Sim-Email`. Execute the workflow API with that header set to a Sim user in another organization: the run bills that user’s org, the owning workspace does not also debit it, and Usage for the billed org shows a By Agent row (workflow, owning org · workspace, Run by). A missing header or malformed email is rejected with 400. An email that matches no user is rejected with 400 and `BILLING_EMAIL_NOT_FOUND`. Remaining credits for the billed org drop by that run.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Daily credit refresh stays off unless the environment explicitly enables it.</t>
+          <t>Signup still creates a personal workspace. `/workspace` fallback still lands somewhere valid.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -2013,17 +2013,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Workflow engine (P1)</t>
+          <t>Billing and workspaces (P0)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>A Response block inside a loop continues the loop. A Response outside a loop ends the workflow.</t>
+          <t>Daily credit refresh stays off unless the environment explicitly enables it.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>An empty `forEach` still runs the block after the loop.</t>
+          <t>A Response block inside a loop continues the loop. A Response outside a loop ends the workflow.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nested loops and nested subflows save and run (upstream rejects these; Arena allows them).</t>
+          <t>An empty `forEach` still runs the block after the loop.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Agent model picker: OpenRouter list is free-only; Azure Anthropic and Arena-added image models still appear where expected.</t>
+          <t>Nested loops and nested subflows save and run (upstream rejects these; Arena allows them).</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Run logs and the console show chart payloads, image payloads, and the acting user.</t>
+          <t>Agent model picker: OpenRouter list is free-only; Azure Anthropic and Arena-added image models still appear where expected.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Extended integrations (P1)</t>
+          <t>Workflow engine (P1)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Slack: Arena Bot (bot token) and Custom Bot (user token) are both selectable. Search, user-channel lookup, and a normal post each succeed. Asking Copilot to connect Slack shows one Connect control (“Connect these, then continue”, button Continue), not a Submit button and not a repeated connect card.</t>
+          <t>Run logs and the console show chart payloads, image payloads, and the acting user.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>HubSpot: on an admin workspace the Accounts picker loads real portals, and a selected account runs a read. `hubspot_get_campaign_metrics` (or another campaign op) plus stock `hubspot_list_contacts` both return data.</t>
+          <t>Slack: Arena Bot (bot token) and Custom Bot (user token) are both selectable. Search, user-channel lookup, and a normal post each succeed. Asking Copilot to connect Slack shows one Connect control (“Connect these, then continue”, button Continue), not a Submit button and not a repeated connect card.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Google Slides: template tables, plus a stock slide action.</t>
+          <t>HubSpot: on an admin workspace the Accounts picker loads real portals, and a selected account runs a read. `hubspot_get_campaign_metrics` (or another campaign op) plus stock `hubspot_list_contacts` both return data.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Zoom: account recordings and transcript download, plus a stock meeting action.</t>
+          <t>Google Slides: template tables, plus a stock slide action.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Shopify: `shopify_list_customers` (assert `success` still available downstream), plus stock `shopify_list_products`.</t>
+          <t>Zoom: account recordings and transcript download, plus a stock meeting action.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Gmail: advanced search and read thread, plus send or read.</t>
+          <t>Shopify: `shopify_list_customers` (assert `success` still available downstream), plus stock `shopify_list_products`.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Google Drive: upload and AI query helpers, plus a stock file read.</t>
+          <t>Gmail: advanced search and read thread, plus send or read.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Image Generator: “Create 3 distinct variations of …” returns three separate images, not one combined frame. Reference images work, and a previously generated image can be picked. Editing that image returns an image preview, not an empty or octet-stream file.</t>
+          <t>Google Drive: upload and AI query helpers, plus a stock file read.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Files (P1)</t>
+          <t>Extended integrations (P1)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Generated images and compiled documents open from the file serve route. Reusing a chat image in a later run copies it onto the run and that file opens (the path is not a broken or context-query URL).</t>
+          <t>Image Generator: “Create 3 distinct variations of …” returns three separate images, not one combined frame. Reference images work, and a previously generated image can be picked. Editing that image returns an image preview, not an empty or octet-stream file.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Org logo upload and display work.</t>
+          <t>Generated images and compiled documents open from the file serve route. Reusing a chat image in a later run copies it onto the run and that file opens (the path is not a broken or context-query URL).</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Editor file upload can pick images already in the chat.</t>
+          <t>Org logo upload and display work.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -2440,22 +2440,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2. Exclusive — Arena-only</t>
+          <t>1. Customized — Sim behavior Arena changed</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Local copilot runtime (P0)</t>
+          <t>Files (P1)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Tool calls, patches, and audit history persist across reload.</t>
+          <t>Editor file upload can pick images already in the chat.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>User access and user memory apply to the next turn.</t>
+          <t>Tool calls, patches, and audit history persist across reload.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Arena task block (P0)</t>
+          <t>Local copilot runtime (P0)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Create task, create task with fields, create sub-task, create sub-task with fields.</t>
+          <t>User access and user memory apply to the next turn.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Add comment, add comment by task number.</t>
+          <t>Create task, create task with fields, create sub-task, create sub-task with fields.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Fetch searched tasks, search task, simple search.</t>
+          <t>Add comment, add comment by task number.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Save summary, get meetings, get token.</t>
+          <t>Fetch searched tasks, search task, simple search.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Get my tasks and get my overdue tasks, from the builder and from a schedule or webhook run. A failure returns an error, not an empty task list.</t>
+          <t>Save summary, get meetings, get token.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Client and project selectors in the block panel load real Arena data.</t>
+          <t>Get my tasks and get my overdue tasks, from the builder and from a schedule or webhook run. A failure returns an error, not an empty task list.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -2661,17 +2661,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Arena Development and generated apps (P1)</t>
+          <t>Arena task block (P0)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>**Arena Development** block: edit an Arena app.</t>
+          <t>Client and project selectors in the block panel load real Arena data.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>**Development** block: generate an app, edit it, and deploy to Vercel.</t>
+          <t>**Arena Development** block: edit an Arena app.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Skill share: publish a skill into the catalog and use the copy in another workspace or org.</t>
+          <t>**Development** block: generate an app, edit it, and deploy to Vercel.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Exclusive blocks (P1)</t>
+          <t>Arena Development and generated apps (P1)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Bing Ads, Facebook Ads, Google Ads V1 (natural-language or GAQL query).</t>
+          <t>Skill share: publish a skill into the catalog and use the copy in another workspace or org.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Figma (file read or design action).</t>
+          <t>Bing Ads, Facebook Ads, Google Ads V1 (natural-language or GAQL query).</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Image Fusion (two or more images in, one fused image out).</t>
+          <t>Figma (file read or design action).</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P2 Docs (template schema, icons, or team data).</t>
+          <t>Image Fusion (two or more images in, one fused image out).</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Semrush and SpyFu (one SEO query each).</t>
+          <t>P2 Docs (template schema, icons, or team data).</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn via Unipile (company or profile read, plus hosted auth / reconnect).</t>
+          <t>Semrush and SpyFu (one SEO query each).</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Chart Generator (ECharts JSON that the chat renderer draws).</t>
+          <t>LinkedIn via Unipile (company or profile read, plus hosted auth / reconnect).</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Cost block (explicit cost on a run shows in usage).</t>
+          <t>Chart Generator (ECharts JSON that the chat renderer draws).</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Skyvern (create or get a run; N/A if this env has no credential).</t>
+          <t>Cost block (explicit cost on a run shows in usage).</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Airweave: one successful run, or N/A with ticket reference (see Section 0).</t>
+          <t>Skyvern (create or get a run; N/A if this env has no credential).</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -3012,17 +3012,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Agents list and video builder (P0)</t>
+          <t>Exclusive blocks (P1)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Global, shared-with-me, and my-agents lists follow email and domain allow-lists. An allowed email sees the agent enabled. An email outside the list sees it disabled or absent for that tab. Undeploying a chat agent removes it from all three lists. An inactive chat does not stay listed.</t>
+          <t>Airweave: one successful run, or N/A with ticket reference (see Section 0).</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Video builder: opening it from the Arena agents list puts the logged-in email on `emailId` and replaces any saved email. Opening that agent when the Arena page omits `emailId` still returns the deployed video builder app. Any other agent without `emailId` is rejected. A Fal call from the video app appears on that Arena user’s usage ledger.</t>
+          <t>Global, shared-with-me, and my-agents lists follow email and domain allow-lists. An allowed email sees the agent enabled. An email outside the list sees it disabled or absent for that tab. Undeploying a chat agent removes it from all three lists. An inactive chat does not stay listed.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Deployed-chat extras that have no upstream equivalent (P0)</t>
+          <t>Agents list and video builder (P0)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Departments, assistant assets, banner messages, prompt feedback, and workflow golden queries.</t>
+          <t>Video builder: opening it from the Arena agents list puts the logged-in email on `emailId` and replaces any saved email. Opening that agent when the Arena page omits `emailId` still returns the deployed video builder app. Any other agent without `emailId` is rejected. A Fal call from the video app appears on that Arena user’s usage ledger.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Thread list in the left nav and theme sync with the Arena shell.</t>
+          <t>Departments, assistant assets, banner messages, prompt feedback, and workflow golden queries.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -3120,17 +3120,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Admin, identity, and ops (P1)</t>
+          <t>Deployed-chat extras that have no upstream equivalent (P0)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Arena SSO modules: login, resume, and legacy cookie clear on a user who still has an old session cookie.</t>
+          <t>Thread list in the left nav and theme sync with the Arena shell.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Settings → Custom OAuth Apps opens and shows the apps form, not a blank section. An org-level app limited to allowed workspaces connects from an allowed workspace.</t>
+          <t>Arena SSO modules: login, resume, and legacy cookie clear on a user who still has an old session cookie.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Platform-admin email can open Settings → Agent access requests, approve one request, and the requester then sees that agent enabled on the agents list.</t>
+          <t>Settings → Custom OAuth Apps opens and shows the apps form, not a blank section. An org-level app limited to allowed workspaces connects from an allowed workspace.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Help and support issue can be filed and is stored.</t>
+          <t>Platform-admin email can open Settings → Agent access requests, approve one request, and the requester then sees that agent enabled on the agents list.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>App banner route and workspace embed page render inside the host frame.</t>
+          <t>Help and support issue can be filed and is stored.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Default workflows import and deploy for a new user.</t>
+          <t>App banner route and workspace embed page render inside the host frame.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>User knowledge base populate still attaches to the user.</t>
+          <t>Default workflows import and deploy for a new user.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Arena general settings (timezone and events) save and apply to chat and copilot.</t>
+          <t>User knowledge base populate still attaches to the user.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Billing package only Arena has (P0)</t>
+          <t>Admin, identity, and ops (P1)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Starter provisioned for a new client org.</t>
+          <t>Arena general settings (timezone and events) save and apply to chat and copilot.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Pro and Max checkout (`team_1950` / `team_6500` catalog).</t>
+          <t>Starter provisioned for a new client org.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Org-admin upgrade comparison overlay.</t>
+          <t>Pro and Max checkout (`team_1950` / `team_6500` catalog).</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Seat reconcile does not fight flat org pricing.</t>
+          <t>Org-admin upgrade comparison overlay.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Usage limit blocks a run when credits are exhausted and allows it when they are not.</t>
+          <t>Seat reconcile does not fight flat org pricing.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>3. Other Sim features — stock regression</t>
+          <t>2. Exclusive — Arena-only</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Builder core (P0)</t>
+          <t>Billing package only Arena has (P0)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Create, rename, duplicate, and delete a workflow. Undo and redo.</t>
+          <t>Usage limit blocks a run when credits are exhausted and allows it when they are not.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Drag blocks, connect edges, and open the editor panel. Variables resolve (`&lt;Block.output&gt;`).</t>
+          <t>Create, rename, duplicate, and delete a workflow. Undo and redo.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Manual run, stop, and read the console. Logs page shows the same run.</t>
+          <t>Drag blocks, connect edges, and open the editor panel. Variables resolve (`&lt;Block.output&gt;`).</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Save and reload. A second user in the same workflow sees realtime updates.</t>
+          <t>Manual run, stop, and read the console. Logs page shows the same run.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Deploy the workflow. API trigger and chat trigger each start a run.</t>
+          <t>Save and reload. A second user in the same workflow sees realtime updates.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Schedule trigger fires once. Webhook trigger accepts one signed request.</t>
+          <t>Deploy the workflow. API trigger and chat trigger each start a run.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Response block returns the configured body. Condition and router take the right branch.</t>
+          <t>Schedule trigger fires once. Webhook trigger accepts one signed request.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Loop and parallel run a small inner graph (in addition to the Arena nested-loop case above).</t>
+          <t>Response block returns the configured body. Condition and router take the right branch.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Workspace surfaces (P2)</t>
+          <t>Builder core (P0)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Home, workflow list, and sidebar navigation.</t>
+          <t>Loop and parallel run a small inner graph (in addition to the Arena nested-loop case above).</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Knowledge: create a base, upload a document, and retrieve it from an Agent block. A hit includes rank. An empty search returns an empty result the Agent can consume, with no crash on a missing rank.</t>
+          <t>Home, workflow list, and sidebar navigation.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Tables: create a table, add a row, filter it.</t>
+          <t>Knowledge: create a base, upload a document, and retrieve it from an Agent block. A hit includes rank. An empty search returns an empty result the Agent can consume, with no crash on a missing rank.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Files: upload, preview (PDF and image), and delete.</t>
+          <t>Tables: create a table, add a row, filter it.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Skills: create and attach one to an agent.</t>
+          <t>Files: upload, preview (PDF and image), and delete.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Logs, tests, dashboards, and changelog pages load.</t>
+          <t>Skills: create and attach one to an agent.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Integrations catalog and a connected credential both open.</t>
+          <t>Logs, tests, dashboards, and changelog pages load.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Recently deleted: restore one workflow.</t>
+          <t>Integrations catalog and a connected credential both open.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Settings that stay on (P2)</t>
+          <t>Workspace surfaces (P2)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Account, teammates, org members, secrets, credential groups.</t>
+          <t>Recently deleted: restore one workflow.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Arena API keys (create, use on an API trigger, revoke).</t>
+          <t>Account, teammates, org members, secrets, credential groups.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Custom tools, MCP tools, MCP servers, sandboxes.</t>
+          <t>Arena API keys (create, use on an API trigger, revoke).</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Permission groups and audit logs, if the org has enterprise.</t>
+          <t>Custom tools, MCP tools, MCP servers, sandboxes.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Subscription page matches the Arena plan from section 1.</t>
+          <t>Permission groups and audit logs, if the org has enterprise.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Agent and model path (P0)</t>
+          <t>Settings that stay on (P2)</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Agent block calls one allowed model and returns text.</t>
+          <t>Subscription page matches the Arena plan from section 1.</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Tools the agent calls show in the trace.</t>
+          <t>Agent block calls one allowed model and returns text.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Memory on an agent survives a second run in the same thread.</t>
+          <t>Tools the agent calls show in the trace.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -4119,17 +4119,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Representative stock integrations (P2)</t>
+          <t>Agent and model path (P0)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Google: Gmail, Calendar, Drive, Sheets, Docs.</t>
+          <t>Memory on an agent survives a second run in the same thread.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Microsoft: Outlook, Teams, OneDrive.</t>
+          <t>Google: Gmail, Calendar, Drive, Sheets, Docs.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Atlassian: Jira, Confluence.</t>
+          <t>Microsoft: Outlook, Teams, OneDrive.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Dev: GitHub, Linear or Jira.</t>
+          <t>Atlassian: Jira, Confluence.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Comms: Slack (stock post), Discord, Microsoft Teams.</t>
+          <t>Dev: GitHub, Linear or Jira.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>CRM: HubSpot or Salesforce (stock read).</t>
+          <t>Comms: Slack (stock post), Discord, Microsoft Teams.</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Data: Airtable or Notion, Postgres or the built-in table.</t>
+          <t>CRM: HubSpot or Salesforce (stock read).</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>AI utilities already in Sim: Search, Function, API block, Evaluator.</t>
+          <t>Data: Airtable or Notion, Postgres or the built-in table.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -4335,17 +4335,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Auth and tenancy (P0)</t>
+          <t>Representative stock integrations (P2)</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Email sign-in and sign-out. Invite a member and accept.</t>
+          <t>AI utilities already in Sim: Search, Function, API block, Evaluator.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>A member cannot open another org’s workspace.</t>
+          <t>Email sign-in and sign-out. Invite a member and accept.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>An archived workspace is not selectable.</t>
+          <t>A member cannot open another org’s workspace.</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -4426,16 +4426,43 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>API key from another workspace is rejected.</t>
+          <t>An archived workspace is not selectable.</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr"/>
     </row>
+    <row r="148" ht="48" customHeight="1">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>3. Other Sim features — stock regression</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Auth and tenancy (P0)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>API key from another workspace is rejected.</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G147"/>
+  <autoFilter ref="A1:G148"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, or N/A" type="list">
+    <dataValidation sqref="F2:F148" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid result" error="Choose Pass, Fail, or N/A" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4475,7 +4502,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -4505,7 +4532,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
